--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0119.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0119.xlsx
@@ -16509,7 +16509,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Ồ, giờ cậu làm nhân viên lau sàn à?! Khéo léo đấy, nhưng đừng hòng thoát khỏi việc bốc hàng dễ thế!</t>
+          <t>Ồ, giờ mày làm nhân viên lau sàn à?! Khéo léo đấy, nhưng đừng hòng thoát khỏi việc bốc hàng dễ thế!</t>
         </is>
       </c>
     </row>
@@ -31459,7 +31459,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Hiểu rồi, ta sẽ theo cậu.</t>
+          <t>Hiểu rồi, tao sẽ theo cậu.</t>
         </is>
       </c>
     </row>
